--- a/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_MOVISTAR ESTUDIANTES.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_MOVISTAR ESTUDIANTES.xlsx
@@ -565,13 +565,13 @@
         <v>24</v>
       </c>
       <c r="D2" t="n">
-        <v>95.5397</v>
+        <v>69.0213</v>
       </c>
       <c r="E2" t="n">
-        <v>79.3779</v>
+        <v>54.4606</v>
       </c>
       <c r="F2" t="n">
-        <v>16.1621</v>
+        <v>14.5609</v>
       </c>
       <c r="G2" t="n">
         <v>42.0098</v>
@@ -610,13 +610,13 @@
         <v>33.2095</v>
       </c>
       <c r="S2" t="n">
-        <v>54.8313</v>
+        <v>28.3131</v>
       </c>
       <c r="T2" t="n">
-        <v>43.623</v>
+        <v>18.7057</v>
       </c>
       <c r="U2" t="n">
-        <v>11.2082</v>
+        <v>9.6075</v>
       </c>
       <c r="V2" t="n">
         <v>-0.5286999999999999</v>
@@ -643,13 +643,13 @@
         <v>22</v>
       </c>
       <c r="D3" t="n">
-        <v>47.9971</v>
+        <v>66.83029999999999</v>
       </c>
       <c r="E3" t="n">
-        <v>40.1461</v>
+        <v>53.1639</v>
       </c>
       <c r="F3" t="n">
-        <v>7.850999999999999</v>
+        <v>13.6661</v>
       </c>
       <c r="G3" t="n">
         <v>22.979</v>
@@ -688,13 +688,13 @@
         <v>35.7193</v>
       </c>
       <c r="S3" t="n">
-        <v>-5.7863</v>
+        <v>13.0468</v>
       </c>
       <c r="T3" t="n">
-        <v>-6.076199999999999</v>
+        <v>6.9415</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2901999999999995</v>
+        <v>6.1055</v>
       </c>
       <c r="V3" t="n">
         <v>46.6368</v>
@@ -721,13 +721,13 @@
         <v>21</v>
       </c>
       <c r="D4" t="n">
-        <v>39.6945</v>
+        <v>49.8821</v>
       </c>
       <c r="E4" t="n">
-        <v>30.3899</v>
+        <v>38.4644</v>
       </c>
       <c r="F4" t="n">
-        <v>9.3048</v>
+        <v>11.4177</v>
       </c>
       <c r="G4" t="n">
         <v>38.4704</v>
@@ -766,13 +766,13 @@
         <v>33.4026</v>
       </c>
       <c r="S4" t="n">
-        <v>3.4598</v>
+        <v>13.6471</v>
       </c>
       <c r="T4" t="n">
-        <v>-2.2428</v>
+        <v>5.8316</v>
       </c>
       <c r="U4" t="n">
-        <v>5.7023</v>
+        <v>7.8156</v>
       </c>
       <c r="V4" t="n">
         <v>-1.8493</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. AMON BYSTROVA</t>
+          <t>F. DIAZ MARTINEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,76 +796,76 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D5" t="n">
-        <v>39.5374</v>
+        <v>43.582</v>
       </c>
       <c r="E5" t="n">
-        <v>37.9639</v>
+        <v>32.1347</v>
       </c>
       <c r="F5" t="n">
-        <v>1.5739</v>
+        <v>11.447</v>
       </c>
       <c r="G5" t="n">
-        <v>23.1524</v>
+        <v>-4.534200000000001</v>
       </c>
       <c r="H5" t="n">
-        <v>18.836</v>
+        <v>-2.539099999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>4.316700000000001</v>
+        <v>-1.9954</v>
       </c>
       <c r="J5" t="n">
-        <v>46.9463</v>
+        <v>26.1645</v>
       </c>
       <c r="K5" t="n">
-        <v>33.6807</v>
+        <v>13.414</v>
       </c>
       <c r="L5" t="n">
-        <v>13.2658</v>
+        <v>12.7505</v>
       </c>
       <c r="M5" t="n">
-        <v>-23.7936</v>
+        <v>-30.6988</v>
       </c>
       <c r="N5" t="n">
-        <v>-14.8446</v>
+        <v>-15.9526</v>
       </c>
       <c r="O5" t="n">
-        <v>-8.949299999999999</v>
+        <v>-14.7458</v>
       </c>
       <c r="P5" t="n">
-        <v>-28.1891</v>
+        <v>11.0056</v>
       </c>
       <c r="Q5" t="n">
-        <v>-56.7654</v>
+        <v>-28.769</v>
       </c>
       <c r="R5" t="n">
-        <v>28.5751</v>
+        <v>39.7741</v>
       </c>
       <c r="S5" t="n">
-        <v>56.2203</v>
+        <v>18.039</v>
       </c>
       <c r="T5" t="n">
-        <v>38.3273</v>
+        <v>10.4835</v>
       </c>
       <c r="U5" t="n">
-        <v>17.8931</v>
+        <v>7.5554</v>
       </c>
       <c r="V5" t="n">
-        <v>-11.646</v>
+        <v>19.0718</v>
       </c>
       <c r="W5" t="n">
-        <v>9.4551</v>
+        <v>24.2553</v>
       </c>
       <c r="X5" t="n">
-        <v>-21.101</v>
+        <v>-5.1835</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>F. DIAZ MARTINEZ</t>
+          <t>H. APARICIO RODRÍGUEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,76 +874,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="D6" t="n">
-        <v>33.1559</v>
+        <v>27.6511</v>
       </c>
       <c r="E6" t="n">
-        <v>25.5017</v>
+        <v>13.8723</v>
       </c>
       <c r="F6" t="n">
-        <v>7.6545</v>
+        <v>13.7792</v>
       </c>
       <c r="G6" t="n">
-        <v>-4.534200000000001</v>
+        <v>17.7592</v>
       </c>
       <c r="H6" t="n">
-        <v>-2.539099999999999</v>
+        <v>7.751</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.9954</v>
+        <v>10.0082</v>
       </c>
       <c r="J6" t="n">
-        <v>26.1645</v>
+        <v>18.4197</v>
       </c>
       <c r="K6" t="n">
-        <v>13.414</v>
+        <v>8.5175</v>
       </c>
       <c r="L6" t="n">
-        <v>12.7505</v>
+        <v>9.9023</v>
       </c>
       <c r="M6" t="n">
-        <v>-30.6988</v>
+        <v>-0.6606000000000002</v>
       </c>
       <c r="N6" t="n">
-        <v>-15.9526</v>
+        <v>-0.7662999999999998</v>
       </c>
       <c r="O6" t="n">
-        <v>-14.7458</v>
+        <v>0.1055</v>
       </c>
       <c r="P6" t="n">
-        <v>11.0056</v>
+        <v>4.8269</v>
       </c>
       <c r="Q6" t="n">
-        <v>-28.769</v>
+        <v>-11.7779</v>
       </c>
       <c r="R6" t="n">
-        <v>39.7741</v>
+        <v>16.6047</v>
       </c>
       <c r="S6" t="n">
-        <v>7.612799999999999</v>
+        <v>3.0206</v>
       </c>
       <c r="T6" t="n">
-        <v>3.8503</v>
+        <v>2.1618</v>
       </c>
       <c r="U6" t="n">
-        <v>3.7625</v>
+        <v>0.8591</v>
       </c>
       <c r="V6" t="n">
-        <v>19.0718</v>
+        <v>2.0444</v>
       </c>
       <c r="W6" t="n">
-        <v>24.2553</v>
+        <v>5.0684</v>
       </c>
       <c r="X6" t="n">
-        <v>-5.1835</v>
+        <v>-3.024</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>H. APARICIO RODRÍGUEZ</t>
+          <t>M. LAGUNA RODRIGUEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,76 +952,76 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="D7" t="n">
-        <v>21.9276</v>
+        <v>17.0999</v>
       </c>
       <c r="E7" t="n">
-        <v>11.2107</v>
+        <v>14.7397</v>
       </c>
       <c r="F7" t="n">
-        <v>10.7167</v>
+        <v>2.3602</v>
       </c>
       <c r="G7" t="n">
-        <v>17.7592</v>
+        <v>8.292399999999999</v>
       </c>
       <c r="H7" t="n">
-        <v>7.751</v>
+        <v>0.1041000000000005</v>
       </c>
       <c r="I7" t="n">
-        <v>10.0082</v>
+        <v>8.188099999999999</v>
       </c>
       <c r="J7" t="n">
-        <v>18.4197</v>
+        <v>18.4547</v>
       </c>
       <c r="K7" t="n">
-        <v>8.5175</v>
+        <v>9.014699999999999</v>
       </c>
       <c r="L7" t="n">
-        <v>9.9023</v>
+        <v>9.4396</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.6606000000000002</v>
+        <v>-10.162</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.7662999999999998</v>
+        <v>-8.9108</v>
       </c>
       <c r="O7" t="n">
-        <v>0.1055</v>
+        <v>-1.2514</v>
       </c>
       <c r="P7" t="n">
-        <v>4.8269</v>
+        <v>1.1586</v>
       </c>
       <c r="Q7" t="n">
-        <v>-11.7779</v>
+        <v>-24.3281</v>
       </c>
       <c r="R7" t="n">
-        <v>16.6047</v>
+        <v>25.4864</v>
       </c>
       <c r="S7" t="n">
-        <v>-2.7031</v>
+        <v>15.9021</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4995999999999999</v>
+        <v>9.9772</v>
       </c>
       <c r="U7" t="n">
-        <v>-2.2033</v>
+        <v>5.924399999999999</v>
       </c>
       <c r="V7" t="n">
-        <v>2.0444</v>
+        <v>-8.252800000000001</v>
       </c>
       <c r="W7" t="n">
-        <v>5.0684</v>
+        <v>10.6357</v>
       </c>
       <c r="X7" t="n">
-        <v>-3.024</v>
+        <v>-18.8885</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. LAGUNA RODRIGUEZ</t>
+          <t>J. SCHILB</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="D8" t="n">
-        <v>19.287</v>
+        <v>11.5362</v>
       </c>
       <c r="E8" t="n">
-        <v>17.3316</v>
+        <v>8.592700000000001</v>
       </c>
       <c r="F8" t="n">
-        <v>1.955</v>
+        <v>2.9434</v>
       </c>
       <c r="G8" t="n">
-        <v>8.292399999999999</v>
+        <v>7.994899999999999</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1041000000000005</v>
+        <v>-2.2821</v>
       </c>
       <c r="I8" t="n">
-        <v>8.188099999999999</v>
+        <v>10.2768</v>
       </c>
       <c r="J8" t="n">
-        <v>18.4547</v>
+        <v>12.9052</v>
       </c>
       <c r="K8" t="n">
-        <v>9.014699999999999</v>
+        <v>0.3424000000000001</v>
       </c>
       <c r="L8" t="n">
-        <v>9.4396</v>
+        <v>12.563</v>
       </c>
       <c r="M8" t="n">
-        <v>-10.162</v>
+        <v>-4.9104</v>
       </c>
       <c r="N8" t="n">
-        <v>-8.9108</v>
+        <v>-2.6247</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.2514</v>
+        <v>-2.2857</v>
       </c>
       <c r="P8" t="n">
-        <v>1.1586</v>
+        <v>-1.7376</v>
       </c>
       <c r="Q8" t="n">
-        <v>-24.3281</v>
+        <v>-12.1641</v>
       </c>
       <c r="R8" t="n">
-        <v>25.4864</v>
+        <v>10.4264</v>
       </c>
       <c r="S8" t="n">
-        <v>18.089</v>
+        <v>6.2613</v>
       </c>
       <c r="T8" t="n">
-        <v>12.5695</v>
+        <v>4.8245</v>
       </c>
       <c r="U8" t="n">
-        <v>5.519600000000001</v>
+        <v>1.4366</v>
       </c>
       <c r="V8" t="n">
-        <v>-8.252800000000001</v>
+        <v>-0.9822000000000001</v>
       </c>
       <c r="W8" t="n">
-        <v>10.6357</v>
+        <v>3.0266</v>
       </c>
       <c r="X8" t="n">
-        <v>-18.8885</v>
+        <v>-4.0087</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. SCHILB</t>
+          <t>D. SANCHEZ PEREZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="D9" t="n">
-        <v>11.7563</v>
+        <v>10.8732</v>
       </c>
       <c r="E9" t="n">
-        <v>9.805899999999999</v>
+        <v>10.1385</v>
       </c>
       <c r="F9" t="n">
-        <v>1.950200000000001</v>
+        <v>0.7343000000000006</v>
       </c>
       <c r="G9" t="n">
-        <v>7.994899999999999</v>
+        <v>1.1574</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.2821</v>
+        <v>1.1619</v>
       </c>
       <c r="I9" t="n">
-        <v>10.2768</v>
+        <v>-0.004899999999998572</v>
       </c>
       <c r="J9" t="n">
-        <v>12.9052</v>
+        <v>26.6739</v>
       </c>
       <c r="K9" t="n">
-        <v>0.3424000000000001</v>
+        <v>16.3503</v>
       </c>
       <c r="L9" t="n">
-        <v>12.563</v>
+        <v>10.3234</v>
       </c>
       <c r="M9" t="n">
-        <v>-4.9104</v>
+        <v>-25.5167</v>
       </c>
       <c r="N9" t="n">
-        <v>-2.6247</v>
+        <v>-15.1883</v>
       </c>
       <c r="O9" t="n">
-        <v>-2.2857</v>
+        <v>-10.3281</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.7376</v>
+        <v>-8.302199999999999</v>
       </c>
       <c r="Q9" t="n">
-        <v>-12.1641</v>
+        <v>-41.7053</v>
       </c>
       <c r="R9" t="n">
-        <v>10.4264</v>
+        <v>33.4024</v>
       </c>
       <c r="S9" t="n">
-        <v>6.4813</v>
+        <v>19.3632</v>
       </c>
       <c r="T9" t="n">
-        <v>6.0381</v>
+        <v>11.9209</v>
       </c>
       <c r="U9" t="n">
-        <v>0.4432</v>
+        <v>7.4424</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.9822000000000001</v>
+        <v>-1.3454</v>
       </c>
       <c r="W9" t="n">
-        <v>3.0266</v>
+        <v>13.2489</v>
       </c>
       <c r="X9" t="n">
-        <v>-4.0087</v>
+        <v>-14.5943</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>D. SANCHEZ PEREZ</t>
+          <t>A. AMON BYSTROVA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D10" t="n">
-        <v>10.4492</v>
+        <v>9.6669</v>
       </c>
       <c r="E10" t="n">
-        <v>8.166599999999999</v>
+        <v>16.3349</v>
       </c>
       <c r="F10" t="n">
-        <v>2.283300000000001</v>
+        <v>-6.668500000000001</v>
       </c>
       <c r="G10" t="n">
-        <v>1.1574</v>
+        <v>23.1524</v>
       </c>
       <c r="H10" t="n">
-        <v>1.1619</v>
+        <v>18.836</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.004899999999998572</v>
+        <v>4.316700000000001</v>
       </c>
       <c r="J10" t="n">
-        <v>26.6739</v>
+        <v>46.9463</v>
       </c>
       <c r="K10" t="n">
-        <v>16.3503</v>
+        <v>33.6807</v>
       </c>
       <c r="L10" t="n">
-        <v>10.3234</v>
+        <v>13.2658</v>
       </c>
       <c r="M10" t="n">
-        <v>-25.5167</v>
+        <v>-23.7936</v>
       </c>
       <c r="N10" t="n">
-        <v>-15.1883</v>
+        <v>-14.8446</v>
       </c>
       <c r="O10" t="n">
-        <v>-10.3281</v>
+        <v>-8.949299999999999</v>
       </c>
       <c r="P10" t="n">
-        <v>-8.302199999999999</v>
+        <v>-28.1891</v>
       </c>
       <c r="Q10" t="n">
-        <v>-41.7053</v>
+        <v>-56.7654</v>
       </c>
       <c r="R10" t="n">
-        <v>33.4024</v>
+        <v>28.5751</v>
       </c>
       <c r="S10" t="n">
-        <v>18.9399</v>
+        <v>26.3492</v>
       </c>
       <c r="T10" t="n">
-        <v>9.948399999999999</v>
+        <v>16.6985</v>
       </c>
       <c r="U10" t="n">
-        <v>8.991299999999999</v>
+        <v>9.6508</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.3454</v>
+        <v>-11.646</v>
       </c>
       <c r="W10" t="n">
-        <v>13.2489</v>
+        <v>9.4551</v>
       </c>
       <c r="X10" t="n">
-        <v>-14.5943</v>
+        <v>-21.101</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>S. GRADIN</t>
+          <t>G. PEREZ HERNANDEZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,70 +1264,70 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="D11" t="n">
-        <v>4.9054</v>
+        <v>9.329800000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>0.2187000000000001</v>
+        <v>7.3169</v>
       </c>
       <c r="F11" t="n">
-        <v>4.6867</v>
+        <v>2.0131</v>
       </c>
       <c r="G11" t="n">
-        <v>1.606</v>
+        <v>10.5356</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.3517</v>
+        <v>11.1014</v>
       </c>
       <c r="I11" t="n">
-        <v>1.9577</v>
+        <v>-0.5653</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.8954</v>
+        <v>22.463</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.9021999999999999</v>
+        <v>16.1464</v>
       </c>
       <c r="L11" t="n">
-        <v>0.006900000000000017</v>
+        <v>6.3171</v>
       </c>
       <c r="M11" t="n">
-        <v>2.5013</v>
+        <v>-11.9271</v>
       </c>
       <c r="N11" t="n">
-        <v>0.5505</v>
+        <v>-5.0448</v>
       </c>
       <c r="O11" t="n">
-        <v>1.9508</v>
+        <v>-6.8822</v>
       </c>
       <c r="P11" t="n">
-        <v>0.1929999999999998</v>
+        <v>-5.02</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.9308</v>
+        <v>-28.962</v>
       </c>
       <c r="R11" t="n">
-        <v>2.1238</v>
+        <v>23.9416</v>
       </c>
       <c r="S11" t="n">
-        <v>1.964</v>
+        <v>2.4207</v>
       </c>
       <c r="T11" t="n">
-        <v>1.9024</v>
+        <v>2.6087</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0616</v>
+        <v>-0.1880000000000001</v>
       </c>
       <c r="V11" t="n">
-        <v>1.1424</v>
+        <v>1.3931</v>
       </c>
       <c r="W11" t="n">
-        <v>1.1424</v>
+        <v>11.2069</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-9.8139</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>9</v>
       </c>
       <c r="D12" t="n">
-        <v>4.0918</v>
+        <v>8.863200000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>0.6492</v>
+        <v>4.5382</v>
       </c>
       <c r="F12" t="n">
-        <v>3.4423</v>
+        <v>4.3251</v>
       </c>
       <c r="G12" t="n">
         <v>8.459099999999999</v>
@@ -1390,13 +1390,13 @@
         <v>3.8616</v>
       </c>
       <c r="S12" t="n">
-        <v>-3.889</v>
+        <v>0.8827999999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>-3.118</v>
+        <v>0.7708</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.7707999999999999</v>
+        <v>0.1120000000000001</v>
       </c>
       <c r="V12" t="n">
         <v>-0.2856000000000001</v>
@@ -1423,13 +1423,13 @@
         <v>14</v>
       </c>
       <c r="D13" t="n">
-        <v>3.345699999999999</v>
+        <v>4.3936</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.4362</v>
+        <v>-1.4431</v>
       </c>
       <c r="F13" t="n">
-        <v>5.7819</v>
+        <v>5.8367</v>
       </c>
       <c r="G13" t="n">
         <v>5.363799999999999</v>
@@ -1468,13 +1468,13 @@
         <v>7.916300000000001</v>
       </c>
       <c r="S13" t="n">
-        <v>0.9935999999999998</v>
+        <v>2.0416</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.1603</v>
+        <v>-0.1674</v>
       </c>
       <c r="U13" t="n">
-        <v>2.1541</v>
+        <v>2.2089</v>
       </c>
       <c r="V13" t="n">
         <v>0.6565</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>I. RODRÍGUEZ GONZÁLEZ</t>
+          <t>S. GRADIN</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,64 +1501,64 @@
         <v>2</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.0693</v>
+        <v>4.1759</v>
       </c>
       <c r="E14" t="n">
-        <v>0.1904</v>
+        <v>-0.7121</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.2596</v>
+        <v>4.888</v>
       </c>
       <c r="G14" t="n">
-        <v>1.15</v>
+        <v>1.606</v>
       </c>
       <c r="H14" t="n">
-        <v>0.248</v>
+        <v>-0.3517</v>
       </c>
       <c r="I14" t="n">
-        <v>0.902</v>
+        <v>1.9577</v>
       </c>
       <c r="J14" t="n">
-        <v>1.3435</v>
+        <v>-0.8954</v>
       </c>
       <c r="K14" t="n">
-        <v>0.0414</v>
+        <v>-0.9021999999999999</v>
       </c>
       <c r="L14" t="n">
-        <v>1.3022</v>
+        <v>0.006900000000000017</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.1936</v>
+        <v>2.5013</v>
       </c>
       <c r="N14" t="n">
-        <v>0.2066</v>
+        <v>0.5505</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.4002</v>
+        <v>1.9508</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.7723</v>
+        <v>0.1929999999999998</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.9654</v>
+        <v>-1.9308</v>
       </c>
       <c r="R14" t="n">
-        <v>0.1931</v>
+        <v>2.1238</v>
       </c>
       <c r="S14" t="n">
-        <v>0.2096</v>
+        <v>1.2345</v>
       </c>
       <c r="T14" t="n">
-        <v>0.4688</v>
+        <v>0.9716</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.2592</v>
+        <v>0.2628</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.6565</v>
+        <v>1.1424</v>
       </c>
       <c r="W14" t="n">
-        <v>-0.6565</v>
+        <v>1.1424</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>D. BABUNASHVILI</t>
+          <t>I. RODRÍGUEZ GONZÁLEZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1576,76 +1576,76 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.8208</v>
+        <v>0.0108</v>
       </c>
       <c r="E15" t="n">
+        <v>-0.0164</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.0272</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.248</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.902</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1.3435</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.0414</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1.3022</v>
+      </c>
+      <c r="M15" t="n">
+        <v>-0.1936</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.2066</v>
+      </c>
+      <c r="O15" t="n">
+        <v>-0.4002</v>
+      </c>
+      <c r="P15" t="n">
+        <v>-0.7723</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>-0.9654</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0.1931</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0.2896</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0.2619</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0.0277</v>
+      </c>
+      <c r="V15" t="n">
+        <v>-0.6565</v>
+      </c>
+      <c r="W15" t="n">
+        <v>-0.6565</v>
+      </c>
+      <c r="X15" t="n">
         <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>-0.8208</v>
-      </c>
-      <c r="G15" t="n">
-        <v>-0.06900000000000001</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-0.2069</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0.1379</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>-0.06900000000000001</v>
-      </c>
-      <c r="N15" t="n">
-        <v>-0.2069</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0.1379</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>-0.1379</v>
-      </c>
-      <c r="T15" t="n">
-        <v>0</v>
-      </c>
-      <c r="U15" t="n">
-        <v>-0.1379</v>
-      </c>
-      <c r="V15" t="n">
-        <v>-0.6138</v>
-      </c>
-      <c r="W15" t="n">
-        <v>0</v>
-      </c>
-      <c r="X15" t="n">
-        <v>-0.6138</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. TUSAMBA SOLIS</t>
+          <t>V. NEGRE FABREGAT</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1654,70 +1654,70 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.1014</v>
+        <v>-0.7060999999999997</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.9799</v>
+        <v>0.7296000000000018</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.1215</v>
+        <v>-1.4359</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.0974</v>
+        <v>-4.933800000000001</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.2759</v>
+        <v>-4.79</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1786</v>
+        <v>-0.1435</v>
       </c>
       <c r="J16" t="n">
-        <v>0.0407</v>
+        <v>11.5082</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>5.359</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0407</v>
+        <v>6.1492</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.1381</v>
+        <v>-16.4417</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.2759</v>
+        <v>-10.149</v>
       </c>
       <c r="O16" t="n">
-        <v>0.1379</v>
+        <v>-6.2925</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.9654</v>
+        <v>-5.4062</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.9654</v>
+        <v>-31.279</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>25.8723</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.0386</v>
+        <v>4.5102</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.0552</v>
+        <v>1.8418</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0166</v>
+        <v>2.6678</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>5.124000000000001</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>18.6582</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-13.5343</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>3</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.3555</v>
+        <v>-0.7087</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1265</v>
+        <v>0.4367999999999999</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.482</v>
+        <v>-1.1455</v>
       </c>
       <c r="G17" t="n">
         <v>0.2773</v>
@@ -1780,13 +1780,13 @@
         <v>0.1931</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.8259</v>
+        <v>-1.1791</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.5519000000000001</v>
+        <v>-0.2416</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.274</v>
+        <v>-0.9375</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>I. CHAMERO CASTELLANOS</t>
+          <t>D. BABUNASHVILI</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1810,76 +1810,76 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.7266</v>
+        <v>-0.8208</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.4419</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.2847</v>
+        <v>-0.8208</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.6429</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.221</v>
+        <v>-0.2069</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.4219</v>
+        <v>0.1379</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.5527</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0.7449</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.2976</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.0903</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.9658</v>
+        <v>-0.2069</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.1243</v>
+        <v>0.1379</v>
       </c>
       <c r="P18" t="n">
-        <v>-2.1239</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.8962</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.7723</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.1875</v>
+        <v>-0.1379</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.2207</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0332</v>
+        <v>-0.1379</v>
       </c>
       <c r="V18" t="n">
-        <v>1.2277</v>
+        <v>-0.6138</v>
       </c>
       <c r="W18" t="n">
-        <v>1.2277</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-0.6138</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>G. PEREZ HERNANDEZ</t>
+          <t>J. TUSAMBA SOLIS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1888,76 +1888,76 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.726299999999999</v>
+        <v>-1.0765</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.4396</v>
+        <v>-0.9799</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.2865</v>
+        <v>-0.09669999999999999</v>
       </c>
       <c r="G19" t="n">
-        <v>10.5356</v>
+        <v>-0.0974</v>
       </c>
       <c r="H19" t="n">
-        <v>11.1014</v>
+        <v>-0.2759</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.5653</v>
+        <v>0.1786</v>
       </c>
       <c r="J19" t="n">
-        <v>22.463</v>
+        <v>0.0407</v>
       </c>
       <c r="K19" t="n">
-        <v>16.1464</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>6.3171</v>
+        <v>0.0407</v>
       </c>
       <c r="M19" t="n">
-        <v>-11.9271</v>
+        <v>-0.1381</v>
       </c>
       <c r="N19" t="n">
-        <v>-5.0448</v>
+        <v>-0.2759</v>
       </c>
       <c r="O19" t="n">
-        <v>-6.8822</v>
+        <v>0.1379</v>
       </c>
       <c r="P19" t="n">
-        <v>-5.02</v>
+        <v>-0.9654</v>
       </c>
       <c r="Q19" t="n">
-        <v>-28.962</v>
+        <v>-0.9654</v>
       </c>
       <c r="R19" t="n">
-        <v>23.9416</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>-10.6353</v>
+        <v>-0.0138</v>
       </c>
       <c r="T19" t="n">
-        <v>-7.1478</v>
+        <v>-0.0552</v>
       </c>
       <c r="U19" t="n">
-        <v>-3.4873</v>
+        <v>0.0414</v>
       </c>
       <c r="V19" t="n">
-        <v>1.3931</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>11.2069</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-9.8139</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>V. NEGRE FABREGAT</t>
+          <t>I. CHAMERO CASTELLANOS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1966,70 +1966,70 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="D20" t="n">
-        <v>-17.9149</v>
+        <v>-2.1598</v>
       </c>
       <c r="E20" t="n">
-        <v>-11.2122</v>
+        <v>-1.9248</v>
       </c>
       <c r="F20" t="n">
-        <v>-6.702599999999999</v>
+        <v>-0.235</v>
       </c>
       <c r="G20" t="n">
-        <v>-4.933800000000001</v>
+        <v>-1.6429</v>
       </c>
       <c r="H20" t="n">
-        <v>-4.79</v>
+        <v>-0.221</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.1435</v>
+        <v>-1.4219</v>
       </c>
       <c r="J20" t="n">
-        <v>11.5082</v>
+        <v>-0.5527</v>
       </c>
       <c r="K20" t="n">
-        <v>5.359</v>
+        <v>0.7449</v>
       </c>
       <c r="L20" t="n">
-        <v>6.1492</v>
+        <v>-1.2976</v>
       </c>
       <c r="M20" t="n">
-        <v>-16.4417</v>
+        <v>-1.0903</v>
       </c>
       <c r="N20" t="n">
-        <v>-10.149</v>
+        <v>-0.9658</v>
       </c>
       <c r="O20" t="n">
-        <v>-6.2925</v>
+        <v>-0.1243</v>
       </c>
       <c r="P20" t="n">
-        <v>-5.4062</v>
+        <v>-2.1239</v>
       </c>
       <c r="Q20" t="n">
-        <v>-31.279</v>
+        <v>-2.8962</v>
       </c>
       <c r="R20" t="n">
-        <v>25.8723</v>
+        <v>0.7723</v>
       </c>
       <c r="S20" t="n">
-        <v>-12.6988</v>
+        <v>0.3793</v>
       </c>
       <c r="T20" t="n">
-        <v>-10.1001</v>
+        <v>0.2964</v>
       </c>
       <c r="U20" t="n">
-        <v>-2.5984</v>
+        <v>0.0829</v>
       </c>
       <c r="V20" t="n">
-        <v>5.124000000000001</v>
+        <v>1.2277</v>
       </c>
       <c r="W20" t="n">
-        <v>18.6582</v>
+        <v>1.2277</v>
       </c>
       <c r="X20" t="n">
-        <v>-13.5343</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2047,19 +2047,19 @@
         <v>26</v>
       </c>
       <c r="D21" t="n">
-        <v>303.9728</v>
+        <v>327.4444</v>
       </c>
       <c r="E21" t="n">
-        <v>241.5693</v>
+        <v>249.8469</v>
       </c>
       <c r="F21" t="n">
-        <v>62.4047</v>
+        <v>77.59649999999999</v>
       </c>
       <c r="G21" t="n">
         <v>177.93</v>
       </c>
       <c r="H21" t="n">
-        <v>76.53589999999998</v>
+        <v>76.5359</v>
       </c>
       <c r="I21" t="n">
         <v>101.3942</v>
@@ -2080,7 +2080,7 @@
         <v>-108.4372</v>
       </c>
       <c r="O21" t="n">
-        <v>-76.3205</v>
+        <v>-76.32050000000001</v>
       </c>
       <c r="P21" t="n">
         <v>-55.9918</v>
@@ -2092,13 +2092,13 @@
         <v>321.4746</v>
       </c>
       <c r="S21" t="n">
-        <v>130.8992</v>
+        <v>154.3703</v>
       </c>
       <c r="T21" t="n">
-        <v>85.5552</v>
+        <v>93.83220000000001</v>
       </c>
       <c r="U21" t="n">
-        <v>45.34500000000001</v>
+        <v>60.53740000000001</v>
       </c>
       <c r="V21" t="n">
         <v>51.1364</v>
